--- a/XGBoost_Outputs/agriculture_cereal_best_xgboost_results.xlsx
+++ b/XGBoost_Outputs/agriculture_cereal_best_xgboost_results.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eskom-my.sharepoint.com/personal/mauduh_eskom_co_za/Documents/Python Projects/Parameter-Optimisation/XGBoost_Outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_2B59D2BFD3D05A0C7D83CCF050BEB0B0709DFE4C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{158C8E7C-12CD-40F4-89E8-4944E315622E}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_2B59D2BFD3D05A0C7D83CCF050BEB0B0709DFE4C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16849215-8794-458B-8CFF-A246E8894DB6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$C$1:$C$7</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -743,6 +746,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="C1:C7" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>